--- a/docentes/Castro Vasquez Julieta - Estadisticos 20232.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20232.xlsx
@@ -594,16 +594,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>97.14</v>
+      </c>
+      <c r="H2">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -617,16 +620,19 @@
         <v>45</v>
       </c>
       <c r="D3">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.56</v>
+      </c>
+      <c r="H3">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -640,16 +646,19 @@
         <v>31</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>31</v>
       </c>
-      <c r="E4">
-        <v>31</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -705,16 +714,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>94.29000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -731,16 +740,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3">
-        <v>93.33</v>
+        <v>95.56</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -766,7 +775,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castro Vasquez Julieta - Estadisticos 20232.xlsx
+++ b/docentes/Castro Vasquez Julieta - Estadisticos 20232.xlsx
@@ -526,7 +526,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -643,7 +643,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -714,16 +714,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>97.14</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -740,16 +740,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G3">
-        <v>95.56</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -760,7 +760,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -769,7 +769,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4">
         <v>100</v>
